--- a/output/archive/MerrivossData/Client_Work/OB11/MV-2022-176/MV-2022-176_AssayWorksheet_072522_R1.xlsx
+++ b/output/archive/MerrivossData/Client_Work/OB11/MV-2022-176/MV-2022-176_AssayWorksheet_072522_R1.xlsx
@@ -482,13 +482,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +505,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -544,12 +545,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Study Director</t>
+          <t>Study lead</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dr M. Larkin</t>
+          <t>Dr M. Larkin (DMPK Study Director)</t>
         </is>
       </c>
     </row>
@@ -607,10 +608,11 @@
         <v>0.031</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Study summary (benchmark)</t>
+          <t>Study summary</t>
         </is>
       </c>
     </row>
@@ -782,6 +784,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -789,15 +792,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.55" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
@@ -809,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -1721,6 +1725,7 @@
         <v>9</v>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -1737,6 +1742,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1745,15 +1751,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1774,10 +1783,20 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Historical mean</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1799,10 +1818,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1824,10 +1851,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1849,10 +1884,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1874,10 +1917,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1899,23 +1950,33 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>within 3-fold of historical mean</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+          <t>µM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.5-2 x historical mean</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>All runs met matrix acceptance criteria. Checked by Helen Marchwood.</t>
+          <t>All accepted runs met matrix acceptance criteria. Checked by Helen Marchwood.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>